--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_330_R33.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_330_R33.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8128</v>
+        <v>5.762</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8144</v>
+        <v>6.125</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.0016</v>
+        <v>-0.363</v>
       </c>
       <c r="G2" t="n">
         <v>2.3502</v>
@@ -610,13 +610,13 @@
         <v>2.5515</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.7232</v>
+        <v>-1.7741</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1791</v>
+        <v>-0.8685</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.5441</v>
+        <v>-0.9056</v>
       </c>
       <c r="V2" t="n">
         <v>7.5054</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6898</v>
+        <v>3.7913</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0871</v>
+        <v>4.323</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3973</v>
+        <v>-0.5317</v>
       </c>
       <c r="G3" t="n">
         <v>3.5614</v>
@@ -688,13 +688,13 @@
         <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9076</v>
+        <v>-0.8061</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.187</v>
+        <v>-0.9510999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2794</v>
+        <v>0.145</v>
       </c>
       <c r="V3" t="n">
         <v>-0.8197</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0568</v>
+        <v>-0.4482</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1576</v>
+        <v>0.2484</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2143</v>
+        <v>-0.6967</v>
       </c>
       <c r="G4" t="n">
-        <v>0.738</v>
+        <v>-0.5775</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4502</v>
+        <v>0.3326</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2878</v>
+        <v>-0.9101</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1284</v>
+        <v>0.0872</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8401999999999999</v>
+        <v>0.0504</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2882</v>
+        <v>0.0368</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3904</v>
+        <v>-0.6647</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.39</v>
+        <v>0.2822</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0004</v>
+        <v>-0.9469</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7929</v>
+        <v>-0.2625</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1889</v>
+        <v>0.1612</v>
       </c>
       <c r="U4" t="n">
-        <v>0.604</v>
+        <v>-0.4237</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.3558</v>
+        <v>-0.5361</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.3558</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>M. NOWELL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.658</v>
+        <v>-0.5956</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0621</v>
+        <v>-0.3363</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5959</v>
+        <v>-0.2593</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5775</v>
+        <v>0.4766</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3326</v>
+        <v>1.1056</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9101</v>
+        <v>-0.6291</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0872</v>
+        <v>0.0371</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0504</v>
+        <v>0.8234</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0368</v>
+        <v>-0.7863</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6647</v>
+        <v>0.4395</v>
       </c>
       <c r="N5" t="n">
         <v>0.2822</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9469</v>
+        <v>0.1573</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4722</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1494</v>
+        <v>-0.3734</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3229</v>
+        <v>0.3734</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. NOWELL</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7301</v>
+        <v>-0.6819</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3363</v>
+        <v>-1.2541</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3938</v>
+        <v>0.5722</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4766</v>
+        <v>1.5728</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1056</v>
+        <v>-0.9902</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6291</v>
+        <v>2.563</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0371</v>
+        <v>1.6196</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8234</v>
+        <v>-0.7359</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7863</v>
+        <v>2.3555</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4395</v>
+        <v>-0.0468</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2822</v>
+        <v>-0.2543</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1573</v>
+        <v>0.2075</v>
       </c>
       <c r="P6" t="n">
+        <v>-1.3917</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-2.3195</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.9278</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.863</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.5542</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.3088</v>
+      </c>
+      <c r="V6" t="n">
         <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-0.1344</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-0.3734</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.239</v>
-      </c>
-      <c r="V6" t="n">
-        <v>-1.0722</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7326</v>
+        <v>-0.7563</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.372</v>
+        <v>0.7604</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6394</v>
+        <v>-1.5168</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5728</v>
+        <v>0.738</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9902</v>
+        <v>0.4502</v>
       </c>
       <c r="I7" t="n">
-        <v>2.563</v>
+        <v>0.2878</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6196</v>
+        <v>2.1284</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7359</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>2.3555</v>
+        <v>1.2882</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0468</v>
+        <v>-1.3904</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2543</v>
+        <v>-0.39</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2075</v>
+        <v>-1.0004</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
         <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9137</v>
+        <v>0.0934</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6721</v>
+        <v>-0.2082</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2416</v>
+        <v>0.3016</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.3558</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.3558</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9348</v>
+        <v>-1.2201</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.716</v>
+        <v>-0.5981</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2187</v>
+        <v>-0.622</v>
       </c>
       <c r="G8" t="n">
         <v>-2.2293</v>
@@ -1078,13 +1078,13 @@
         <v>2.0876</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4736</v>
+        <v>-0.7589</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.5525</v>
+        <v>-1.4345</v>
       </c>
       <c r="U8" t="n">
-        <v>1.0789</v>
+        <v>0.6757</v>
       </c>
       <c r="V8" t="n">
         <v>1.0722</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3506</v>
+        <v>-1.697</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2054</v>
+        <v>-0.4846</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1452</v>
+        <v>-1.2124</v>
       </c>
       <c r="G9" t="n">
         <v>0.0062</v>
@@ -1156,13 +1156,13 @@
         <v>1.6237</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4112</v>
+        <v>0.0648</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.2989</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1669</v>
+        <v>-0.2341</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0722</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4566</v>
+        <v>-2.7337</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1871</v>
+        <v>-1.0691</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2695</v>
+        <v>-1.6646</v>
       </c>
       <c r="G10" t="n">
         <v>-1.353</v>
@@ -1234,13 +1234,13 @@
         <v>2.0876</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.034</v>
+        <v>-1.3111</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2538</v>
+        <v>-1.1358</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7802</v>
+        <v>-0.1753</v>
       </c>
       <c r="V10" t="n">
         <v>0.3943</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.205500000000001</v>
+        <v>-8.6692</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.6358</v>
+        <v>-6.797</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5698</v>
+        <v>-1.8722</v>
       </c>
       <c r="G11" t="n">
         <v>-3.4955</v>
@@ -1312,13 +1312,13 @@
         <v>1.8556</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6225000000000001</v>
+        <v>-1.0862</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.55</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0725</v>
+        <v>-0.3749</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0722</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.6224</v>
+        <v>-7.2487</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5444000000000004</v>
+        <v>0.917600000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.166700000000001</v>
+        <v>-8.166499999999999</v>
       </c>
       <c r="G12" t="n">
         <v>1.049900000000001</v>
@@ -1390,13 +1390,13 @@
         <v>15.077</v>
       </c>
       <c r="S12" t="n">
-        <v>-7.0771</v>
+        <v>-6.7037</v>
       </c>
       <c r="T12" t="n">
-        <v>-6.150300000000001</v>
+        <v>-5.7768</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9269000000000002</v>
+        <v>-0.9267000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>3.0437</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.184799999999999</v>
+        <v>7.9782</v>
       </c>
       <c r="E13" t="n">
-        <v>6.2301</v>
+        <v>6.1122</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9547</v>
+        <v>1.866</v>
       </c>
       <c r="G13" t="n">
         <v>1.6216</v>
@@ -1468,13 +1468,13 @@
         <v>3.7112</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4963</v>
+        <v>1.2896</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2363</v>
+        <v>0.1184</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2599</v>
+        <v>1.1712</v>
       </c>
       <c r="V13" t="n">
         <v>1.3558</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4165</v>
+        <v>4.5053</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9961</v>
+        <v>3.4679</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4204</v>
+        <v>1.0374</v>
       </c>
       <c r="G14" t="n">
         <v>2.8796</v>
@@ -1546,13 +1546,13 @@
         <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2464</v>
+        <v>0.8424</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8804</v>
+        <v>-0.4086</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6339</v>
+        <v>1.2509</v>
       </c>
       <c r="V14" t="n">
         <v>-1.0722</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1704</v>
+        <v>3.5857</v>
       </c>
       <c r="E15" t="n">
         <v>1.2874</v>
       </c>
       <c r="F15" t="n">
-        <v>1.883</v>
+        <v>2.2984</v>
       </c>
       <c r="G15" t="n">
         <v>-0.2321</v>
@@ -1624,13 +1624,13 @@
         <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7789</v>
+        <v>1.1942</v>
       </c>
       <c r="T15" t="n">
         <v>-0.3102</v>
       </c>
       <c r="U15" t="n">
-        <v>1.089</v>
+        <v>1.5044</v>
       </c>
       <c r="V15" t="n">
         <v>0.5361</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6678</v>
+        <v>1.9874</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6703</v>
+        <v>0.7883</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9975000000000001</v>
+        <v>1.1992</v>
       </c>
       <c r="G16" t="n">
         <v>-0.3434</v>
@@ -1702,13 +1702,13 @@
         <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3154</v>
+        <v>0.635</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4955</v>
+        <v>0.6135</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1801</v>
+        <v>0.0215</v>
       </c>
       <c r="V16" t="n">
         <v>0.5361</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1415</v>
+        <v>0.4345</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8644</v>
+        <v>1.3926</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7229</v>
+        <v>-0.9581</v>
       </c>
       <c r="G17" t="n">
         <v>0.6801</v>
@@ -1780,13 +1780,13 @@
         <v>0.4639</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0697</v>
+        <v>0.3626</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5623</v>
+        <v>0.0905</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5074</v>
+        <v>0.2721</v>
       </c>
       <c r="V17" t="n">
         <v>-1.0722</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2012</v>
+        <v>0.3893</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6379</v>
+        <v>1.4635</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.839</v>
+        <v>-1.0743</v>
       </c>
       <c r="G18" t="n">
         <v>-0.0389</v>
@@ -1858,13 +1858,13 @@
         <v>2.7834</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0901</v>
+        <v>0.5004</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8136</v>
+        <v>0.0121</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7235</v>
+        <v>0.4883</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5361</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. BOLOMBOY</t>
+          <t>C. MILLER-MCINTYRE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4997</v>
+        <v>-0.722</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9906</v>
+        <v>-1.0516</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4908</v>
+        <v>0.3295</v>
       </c>
       <c r="G19" t="n">
-        <v>-5.1534</v>
+        <v>0.6872</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.1057</v>
+        <v>-1.5981</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.0476</v>
+        <v>2.2853</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.9306</v>
+        <v>2.4742</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.0411</v>
+        <v>-1.2899</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1104</v>
+        <v>3.764</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.2227</v>
+        <v>-1.7869</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.3082</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.1581</v>
+        <v>-1.4787</v>
       </c>
       <c r="P19" t="n">
         <v>0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6237</v>
+        <v>3.9432</v>
       </c>
       <c r="S19" t="n">
-        <v>3.6537</v>
+        <v>0.6655</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5637</v>
+        <v>-0.1883</v>
       </c>
       <c r="U19" t="n">
-        <v>1.0899</v>
+        <v>0.8538</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5361</v>
+        <v>-2.5387</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5361</v>
+        <v>0.1418</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2112</v>
+        <v>-0.9589</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4145</v>
+        <v>0.5324</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6257</v>
+        <v>-1.4913</v>
       </c>
       <c r="G20" t="n">
         <v>-1.3759</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0228</v>
+        <v>0.2752</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0668</v>
+        <v>0.0512</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0896</v>
+        <v>0.224</v>
       </c>
       <c r="V20" t="n">
         <v>0.1418</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. MILLER-MCINTYRE</t>
+          <t>J. BOLOMBOY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6929</v>
+        <v>-2.4028</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4054</v>
+        <v>-2.5239</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2875</v>
+        <v>0.1212</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6872</v>
+        <v>-5.1534</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.5981</v>
+        <v>-3.1057</v>
       </c>
       <c r="I21" t="n">
-        <v>2.2853</v>
+        <v>-2.0476</v>
       </c>
       <c r="J21" t="n">
-        <v>2.4742</v>
+        <v>-2.9306</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2899</v>
+        <v>-3.0411</v>
       </c>
       <c r="L21" t="n">
-        <v>3.764</v>
+        <v>0.1104</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7869</v>
+        <v>-2.2227</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3082</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.4787</v>
+        <v>-2.1581</v>
       </c>
       <c r="P21" t="n">
         <v>0.4639</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>3.9432</v>
+        <v>1.6237</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3053</v>
+        <v>1.7506</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5421</v>
+        <v>1.0304</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2368</v>
+        <v>0.7202</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.5387</v>
+        <v>0.5361</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1418</v>
+        <v>0.5361</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.6805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9343</v>
+        <v>-2.4967</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5555</v>
+        <v>-1.3196</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3788</v>
+        <v>-1.1772</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9144</v>
@@ -2170,13 +2170,13 @@
         <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3962</v>
+        <v>0.0413</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2908</v>
+        <v>-0.0549</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1054</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4195</v>
+        <v>-3.105</v>
       </c>
       <c r="E23" t="n">
         <v>-2.5187</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9008</v>
+        <v>-0.5863</v>
       </c>
       <c r="G23" t="n">
         <v>1.1395</v>
@@ -2248,13 +2248,13 @@
         <v>1.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7784</v>
+        <v>1.093</v>
       </c>
       <c r="T23" t="n">
         <v>-0.0272</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8057</v>
+        <v>1.1202</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9304</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>7.622199999999999</v>
+        <v>9.195</v>
       </c>
       <c r="E24" t="n">
         <v>7.630500000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.008299999999999974</v>
+        <v>1.564500000000001</v>
       </c>
       <c r="G24" t="n">
         <v>-1.0501</v>
@@ -2296,13 +2296,13 @@
         <v>2.1117</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.161799999999999</v>
+        <v>-3.1618</v>
       </c>
       <c r="J24" t="n">
         <v>11.4219</v>
       </c>
       <c r="K24" t="n">
-        <v>2.187800000000001</v>
+        <v>2.1878</v>
       </c>
       <c r="L24" t="n">
         <v>9.233799999999999</v>
@@ -2311,7 +2311,7 @@
         <v>-12.4717</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.07589999999999997</v>
+        <v>-0.07590000000000002</v>
       </c>
       <c r="O24" t="n">
         <v>-12.3956</v>
@@ -2326,16 +2326,16 @@
         <v>19.716</v>
       </c>
       <c r="S24" t="n">
-        <v>7.077199999999999</v>
+        <v>8.649799999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>0.9266999999999997</v>
+        <v>0.9269000000000002</v>
       </c>
       <c r="U24" t="n">
-        <v>6.1502</v>
+        <v>7.722799999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.0437</v>
+        <v>-3.043700000000001</v>
       </c>
       <c r="W24" t="n">
         <v>10.3588</v>
